--- a/PHRS_Acil_Sertifikalar.xlsx
+++ b/PHRS_Acil_Sertifikalar.xlsx
@@ -1263,27 +1263,27 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>AFER</t>
+          <t>ABALFADHEL</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>8913332</t>
+          <t>9884100</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>PANAMA</t>
+          <t>IRAQ</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>MLC (Maritime Labour Certificate)</t>
+          <t>ISSC (International Ship Security Certificate)</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>06/11/2024</t>
+          <t>23/03/2026</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1295,27 +1295,27 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>AFER</t>
+          <t>ABALFADHEL</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>8913332</t>
+          <t>9884100</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>PANAMA</t>
+          <t>IRAQ</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>SMC (Safety Management Certificate)</t>
+          <t>MLC (Maritime Labour Certificate)</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>07/02/2022</t>
+          <t>23/03/2026</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1327,17 +1327,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>AFER</t>
+          <t>ABALFADHEL</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>8913332</t>
+          <t>9884100</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>PANAMA</t>
+          <t>IRAQ</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>28/10/2024</t>
+          <t>23/03/2026</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1359,27 +1359,27 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>AFER</t>
+          <t>ABLE</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>8913332</t>
+          <t>9001136</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>PANAMA</t>
+          <t>PALAU</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>SMC (Safety Management Certificate)</t>
+          <t>BWM (International Ballast Water Management Certificate)</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>06/11/2024</t>
+          <t>03/04/2025</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1391,12 +1391,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>AGN LAGERTHA</t>
+          <t>ABLE</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>9013000</t>
+          <t>9001136</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1406,12 +1406,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>BWM (International Ballast Water Management Certificate)</t>
+          <t>CL (Certificate of Classification )</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>20/03/2026</t>
+          <t>14/04/2022</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1423,12 +1423,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>AGN LAGERTHA</t>
+          <t>ABLE</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>9013000</t>
+          <t>9001136</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1438,12 +1438,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>CL (Certificate of Classification)</t>
+          <t>IAPP (International Air Pollution Prevention Certificate)</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>13/06/2026</t>
+          <t>14/04/2022</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1455,12 +1455,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>AGN LAGERTHA</t>
+          <t>ABLE</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>9013000</t>
+          <t>9001136</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1470,12 +1470,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>DANG (Certificate of Compliance with Special Requirements for Ships Carrying Dangerous Goods)</t>
+          <t>IHM (Statement of Compliance on Inventory of Hazardous Materials)</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>20/03/2026</t>
+          <t>14/04/2022</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1487,12 +1487,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>AGN LAGERTHA</t>
+          <t>ABLE</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>9013000</t>
+          <t>9001136</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1502,12 +1502,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>IAFSC (International Anti-Fouling System Certificate)</t>
+          <t>IMSBC (Document of Compliance for the Carriage of Solid Bulk Cargoes)</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>20/03/2026</t>
+          <t>14/04/2022</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1519,12 +1519,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>AGN LAGERTHA</t>
+          <t>ABLE</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>9013000</t>
+          <t>9001136</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1534,12 +1534,12 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>IAPPC (International Air Pollution Prevention Certificate)</t>
+          <t>IOPP (International Oil Pollution Prevention Certificate)</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>13/06/2026</t>
+          <t>24/03/2023</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1551,12 +1551,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>AGN LAGERTHA</t>
+          <t>ABLE</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>9013000</t>
+          <t>9001136</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>IEEC (International Energy Efficiency Certificate)</t>
+          <t>ISPP (International Sewage Pollution Prevention Certificate)</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>20/03/2026</t>
+          <t>14/04/2022</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1583,12 +1583,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>AGN LAGERTHA</t>
+          <t>ABLE</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>9013000</t>
+          <t>9001136</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>IHM (Statement of Compliance on Inventory of Hazardous Materials)</t>
+          <t>ISSC (International Ship Security Certificate)</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>20/03/2026</t>
+          <t>14/07/2022</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1615,12 +1615,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>AGN LAGERTHA</t>
+          <t>ABLE</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>9013000</t>
+          <t>9001136</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1630,12 +1630,12 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>IMSBC (Interim Document of Compliance for the Carriage of Solid Bulk Cargoes (with EXE))</t>
+          <t>ISSC (International Ship Security Certificate)</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>20/03/2026</t>
+          <t>19/04/2025</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1647,12 +1647,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>AGN LAGERTHA</t>
+          <t>ABLE</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>9013000</t>
+          <t>9001136</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1662,12 +1662,12 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>IOPP (International Oil Pollution Prevention Certificate - Other than Oil Tanker)</t>
+          <t>LL (International Load Line Certificate)</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>20/03/2026</t>
+          <t>14/04/2022</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1679,12 +1679,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>AGN LAGERTHA</t>
+          <t>ABLE</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>9013000</t>
+          <t>9001136</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1694,12 +1694,12 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>ISPP (International Sewage Pollution Prevention Certificate)</t>
+          <t>MLC (Maritime Labour Certificate)</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>20/03/2026</t>
+          <t>14/07/2022</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1711,12 +1711,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>AGN LAGERTHA</t>
+          <t>ABLE</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>9013000</t>
+          <t>9001136</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>ISPP (International Sewage Pollution Prevention Certificate)</t>
+          <t>MLC (Maritime Labour Certificate)</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>19/04/2025</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1743,12 +1743,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>AGN LAGERTHA</t>
+          <t>ABLE</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>9013000</t>
+          <t>9001136</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1758,12 +1758,12 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>ISSC (International Ship Security Certificate)</t>
+          <t>SC (Cargo Ship Safety Construction Certificate)</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>20/03/2026</t>
+          <t>14/04/2022</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1775,12 +1775,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>AGN LAGERTHA</t>
+          <t>ABLE</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>9013000</t>
+          <t>9001136</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1790,12 +1790,12 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>ITC (International Tonnage Certificate)</t>
+          <t>SE (Cargo Ship Safety Equipment Certificate)</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>20/03/2026</t>
+          <t>14/04/2022</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1807,12 +1807,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>AGN LAGERTHA</t>
+          <t>ABLE</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>9013000</t>
+          <t>9001136</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1822,12 +1822,12 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LL ( International Load Line Certificate )</t>
+          <t>SMC (Safety Management Certificate)</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>20/03/2026</t>
+          <t>14/07/2022</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1839,12 +1839,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>AGN LAGERTHA</t>
+          <t>ABLE</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>9013000</t>
+          <t>9001136</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1854,12 +1854,12 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>MLC (Maritime Labour Certificate)</t>
+          <t>SMC (Safety Management Certificate)</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>20/03/2026</t>
+          <t>16/05/2024</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -1871,12 +1871,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>AGN LAGERTHA</t>
+          <t>ABLE</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>9013000</t>
+          <t>9001136</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>SC (Cargo Ship Safety Construction Certificate)</t>
+          <t>SMC (Safety Management Certificate)</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>13/06/2026</t>
+          <t>19/04/2025</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -1903,12 +1903,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>AGN LAGERTHA</t>
+          <t>ABLE</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>9013000</t>
+          <t>9001136</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>SE (Cargo Ship Safety Equipment Certificate)</t>
+          <t>SR (Cargo Ship Safety Radio Certificate)</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>30/03/2026</t>
+          <t>14/04/2022</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -1935,27 +1935,27 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>AGN LAGERTHA</t>
+          <t>ABLE</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>9013000</t>
+          <t>9001136</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>PALAU</t>
+          <t>PANAMA</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>SMC (Safety Management Certificate)</t>
+          <t>ISSC (International Ship Security Certificate)</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>20/03/2026</t>
+          <t>16/08/2021</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -1967,27 +1967,27 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>AGN LAGERTHA</t>
+          <t>ADA ZEYNEP</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>9013000</t>
+          <t>8947876</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>PALAU</t>
+          <t>TURKEY</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>SR (Cargo Ship Safety Radio Certificate)</t>
+          <t>CL (Certificate of Classification)</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>20/03/2026</t>
+          <t>05/03/2025</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -1999,12 +1999,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>AGN RAGNAR</t>
+          <t>ADELHEID BR</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>9148104</t>
+          <t>9387621</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2014,12 +2014,12 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>BWM (International Ballast Water Management Certificate)</t>
+          <t>ISSC (International Ship Security Certificate)</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>01/07/2026</t>
+          <t>25/02/2026</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2031,12 +2031,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>AGN RAGNAR</t>
+          <t>ADELHEID BR</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>9148104</t>
+          <t>9387621</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2046,12 +2046,12 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>CL (Certificate of Classification)</t>
+          <t>MLC (Maritime Labour Certificate)</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>01/07/2026</t>
+          <t>25/02/2026</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2063,27 +2063,27 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>ABALFADHEL</t>
+          <t>AGN RAGNAR</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>9884100</t>
+          <t>9148104</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>IRAQ</t>
+          <t>PALAU</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>ISSC (International Ship Security Certificate)</t>
+          <t>DANG (Certificate of Compliance with Special Requirements for Ships Carrying Dangerous Goods)</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>01/07/2026</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2095,27 +2095,27 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>ABALFADHEL</t>
+          <t>AGN RAGNAR</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>9884100</t>
+          <t>9148104</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>IRAQ</t>
+          <t>PALAU</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>MLC (Maritime Labour Certificate)</t>
+          <t>IAFSC (International Anti-Fouling System Certificate)</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>01/07/2026</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2127,27 +2127,27 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>ABALFADHEL</t>
+          <t>AGN RAGNAR</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>9884100</t>
+          <t>9148104</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>IRAQ</t>
+          <t>PALAU</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>SMC (Safety Management Certificate)</t>
+          <t>IAPPC (International Air Pollution Prevention Certificate)</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>01/07/2026</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2159,12 +2159,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>ABLE</t>
+          <t>AGN RAGNAR</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>9001136</t>
+          <t>9148104</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>BWM (International Ballast Water Management Certificate)</t>
+          <t>IHM (Statement of Compliance on Inventory of Hazardous Materials)</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>03/04/2025</t>
+          <t>01/07/2026</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2191,12 +2191,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>ABLE</t>
+          <t>AGN RAGNAR</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>9001136</t>
+          <t>9148104</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2206,12 +2206,12 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>CL (Certificate of Classification )</t>
+          <t>IMSBC (Document of Compliance for the Carriage of Solid Bulk Cargoes)</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>14/04/2022</t>
+          <t>01/07/2026</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2223,12 +2223,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>ABLE</t>
+          <t>AGN RAGNAR</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>9001136</t>
+          <t>9148104</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2238,12 +2238,12 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>IAPP (International Air Pollution Prevention Certificate)</t>
+          <t>IOPP (International Oil Pollution Prevention Certificate - Other than Oil Tanker)</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>14/04/2022</t>
+          <t>01/07/2026</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2255,12 +2255,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>ABLE</t>
+          <t>AGN RAGNAR</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>9001136</t>
+          <t>9148104</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2270,12 +2270,12 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>IHM (Statement of Compliance on Inventory of Hazardous Materials)</t>
+          <t>ISPP (International Sewage Pollution Prevention Certificate)</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>14/04/2022</t>
+          <t>01/07/2026</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2287,12 +2287,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>ABLE</t>
+          <t>AGN RAGNAR</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>9001136</t>
+          <t>9148104</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>IMSBC (Document of Compliance for the Carriage of Solid Bulk Cargoes)</t>
+          <t>ISSC (International Ship Security Certificate)</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>14/04/2022</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2319,12 +2319,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>ABLE</t>
+          <t>AGN RAGNAR</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>9001136</t>
+          <t>9148104</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2334,12 +2334,12 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>IOPP (International Oil Pollution Prevention Certificate)</t>
+          <t>LL (International Load Line Certificate)</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>24/03/2023</t>
+          <t>01/07/2026</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2351,12 +2351,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>ABLE</t>
+          <t>AGN RAGNAR</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>9001136</t>
+          <t>9148104</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2366,12 +2366,12 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>ISPP (International Sewage Pollution Prevention Certificate)</t>
+          <t>MLC (Maritime Labour Certificate)</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>14/04/2022</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2383,12 +2383,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>ABLE</t>
+          <t>AGN RAGNAR</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>9001136</t>
+          <t>9148104</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2398,12 +2398,12 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>ISSC (International Ship Security Certificate)</t>
+          <t>SC (Cargo Ship Safety Construction Certificate)</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>14/07/2022</t>
+          <t>01/07/2026</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2415,12 +2415,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>ABLE</t>
+          <t>AGN RAGNAR</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>9001136</t>
+          <t>9148104</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2430,12 +2430,12 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>ISSC (International Ship Security Certificate)</t>
+          <t>SE (Cargo Ship Safety Equipment Certificate)</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>19/04/2025</t>
+          <t>01/07/2026</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2447,12 +2447,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>ABLE</t>
+          <t>AGN RAGNAR</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>9001136</t>
+          <t>9148104</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2462,12 +2462,12 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LL (International Load Line Certificate)</t>
+          <t>SMC (Safety Management Certificate)</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>14/04/2022</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2479,12 +2479,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>ABLE</t>
+          <t>AGN RAGNAR</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>9001136</t>
+          <t>9148104</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2494,12 +2494,12 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>MLC (Maritime Labour Certificate)</t>
+          <t>SR (Cargo Ship Safety Radio Certificate)</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>14/07/2022</t>
+          <t>01/07/2026</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2511,27 +2511,27 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>ABLE</t>
+          <t>AGRAFENA</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>9001136</t>
+          <t>9100097</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>PALAU</t>
+          <t>PANAMA</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>MLC (Maritime Labour Certificate)</t>
+          <t>CICA (Certificate of Inspection of Crew Accommodation)</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>19/04/2025</t>
+          <t>15/03/2024</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2543,27 +2543,27 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>ABLE</t>
+          <t>AGRAFENA</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>9001136</t>
+          <t>9100097</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>PALAU</t>
+          <t>PANAMA</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>SC (Cargo Ship Safety Construction Certificate)</t>
+          <t>CICA (Certificate of Inspection of Crew Accommodation)</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>14/04/2022</t>
+          <t>11/11/2025</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2575,27 +2575,27 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>ABLE</t>
+          <t>AHMET CAN</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>9001136</t>
+          <t>9368182</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>PALAU</t>
+          <t>PANAMA</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>SE (Cargo Ship Safety Equipment Certificate)</t>
+          <t>BWM (International Ballast Water Management Certificate)</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>14/04/2022</t>
+          <t>15/04/2024</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2607,27 +2607,27 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>ABLE</t>
+          <t>AHMET CAN</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>9001136</t>
+          <t>9368182</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>PALAU</t>
+          <t>PANAMA</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>SMC (Safety Management Certificate)</t>
+          <t>CICA (Certificate of Inspection of Crew Accommodation)</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>14/07/2022</t>
+          <t>07/07/2023</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2639,27 +2639,27 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>ABLE</t>
+          <t>AHMET CAN</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>9001136</t>
+          <t>9368182</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>PALAU</t>
+          <t>PANAMA</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>SMC (Safety Management Certificate)</t>
+          <t>DANG (Certificate of Compliance with Special Requirements for Ships Carrying Dangerous Goods)</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>16/05/2024</t>
+          <t>08/04/2024</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2671,27 +2671,27 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>ABLE</t>
+          <t>AHMET CAN</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>9001136</t>
+          <t>9368182</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>PALAU</t>
+          <t>PANAMA</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>SMC (Safety Management Certificate)</t>
+          <t>GPP (Garbage Pollution Prevention Statement of Compliance)</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>19/04/2025</t>
+          <t>08/04/2024</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2703,27 +2703,27 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>ABLE</t>
+          <t>AHMET CAN</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>9001136</t>
+          <t>9368182</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>PALAU</t>
+          <t>PANAMA</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>SR (Cargo Ship Safety Radio Certificate)</t>
+          <t>IAPP (International Air Pollution Prevention Certificate)</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>14/04/2022</t>
+          <t>08/04/2024</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2735,12 +2735,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>ABLE</t>
+          <t>AHMET CAN</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>9001136</t>
+          <t>9368182</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>ISSC (International Ship Security Certificate)</t>
+          <t>IHM (Statement of Compliance on Inventory of Hazardous Materials)</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>16/08/2021</t>
+          <t>15/04/2024</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2767,27 +2767,27 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>ADA ZEYNEP</t>
+          <t>AHMET CAN</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>8947876</t>
+          <t>9368182</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>TURKEY</t>
+          <t>PANAMA</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>CL (Certificate of Classification)</t>
+          <t>IMSBC (Document of Compliance for the Carriage of Solid Bulk Cargoes)</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>05/03/2025</t>
+          <t>08/04/2024</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -2799,27 +2799,27 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>ADELHEID BR</t>
+          <t>AHMET CAN</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>9387621</t>
+          <t>9368182</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>PALAU</t>
+          <t>PANAMA</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>ISSC (International Ship Security Certificate)</t>
+          <t>IOPP (International Oil Pollution Prevention Certificate)</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>25/02/2026</t>
+          <t>08/04/2024</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -2831,27 +2831,27 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>ADELHEID BR</t>
+          <t>AHMET CAN</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>9387621</t>
+          <t>9368182</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>PALAU</t>
+          <t>PANAMA</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>MLC (Maritime Labour Certificate)</t>
+          <t>ISPP (International Sewage Pollution Prevention Certificate)</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>25/02/2026</t>
+          <t>08/04/2024</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -2863,27 +2863,27 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>AGN RAGNAR</t>
+          <t>AFER</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>9148104</t>
+          <t>8913332</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>PALAU</t>
+          <t>PANAMA</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>DANG (Certificate of Compliance with Special Requirements for Ships Carrying Dangerous Goods)</t>
+          <t>MLC (Maritime Labour Certificate)</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>01/07/2026</t>
+          <t>06/11/2024</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -2895,27 +2895,27 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>AGN RAGNAR</t>
+          <t>AFER</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>9148104</t>
+          <t>8913332</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>PALAU</t>
+          <t>PANAMA</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>IAFSC (International Anti-Fouling System Certificate)</t>
+          <t>SMC (Safety Management Certificate)</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>01/07/2026</t>
+          <t>07/02/2022</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -2927,27 +2927,27 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>AGN RAGNAR</t>
+          <t>AFER</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>9148104</t>
+          <t>8913332</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>PALAU</t>
+          <t>PANAMA</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>IAPPC (International Air Pollution Prevention Certificate)</t>
+          <t>SMC (Safety Management Certificate)</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>01/07/2026</t>
+          <t>28/10/2024</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -2959,27 +2959,27 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>AGN RAGNAR</t>
+          <t>AFER</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>9148104</t>
+          <t>8913332</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>PALAU</t>
+          <t>PANAMA</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>IHM (Statement of Compliance on Inventory of Hazardous Materials)</t>
+          <t>SMC (Safety Management Certificate)</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>01/07/2026</t>
+          <t>06/11/2024</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -2991,12 +2991,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>AGN RAGNAR</t>
+          <t>AGN LAGERTHA</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>9148104</t>
+          <t>9013000</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3006,12 +3006,12 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>IMSBC (Document of Compliance for the Carriage of Solid Bulk Cargoes)</t>
+          <t>BWM (International Ballast Water Management Certificate)</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>01/07/2026</t>
+          <t>20/03/2026</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3023,12 +3023,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>AGN RAGNAR</t>
+          <t>AGN LAGERTHA</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>9148104</t>
+          <t>9013000</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>IOPP (International Oil Pollution Prevention Certificate - Other than Oil Tanker)</t>
+          <t>CL (Certificate of Classification)</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>01/07/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3055,12 +3055,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>AGN RAGNAR</t>
+          <t>AGN LAGERTHA</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>9148104</t>
+          <t>9013000</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -3070,12 +3070,12 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>ISPP (International Sewage Pollution Prevention Certificate)</t>
+          <t>DANG (Certificate of Compliance with Special Requirements for Ships Carrying Dangerous Goods)</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>01/07/2026</t>
+          <t>20/03/2026</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3087,12 +3087,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>AGN RAGNAR</t>
+          <t>AGN LAGERTHA</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>9148104</t>
+          <t>9013000</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3102,12 +3102,12 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>ISSC (International Ship Security Certificate)</t>
+          <t>IAFSC (International Anti-Fouling System Certificate)</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>20/03/2026</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3119,12 +3119,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>AGN RAGNAR</t>
+          <t>AGN LAGERTHA</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>9148104</t>
+          <t>9013000</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LL (International Load Line Certificate)</t>
+          <t>IAPPC (International Air Pollution Prevention Certificate)</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>01/07/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3151,12 +3151,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>AGN RAGNAR</t>
+          <t>AGN LAGERTHA</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>9148104</t>
+          <t>9013000</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>MLC (Maritime Labour Certificate)</t>
+          <t>IEEC (International Energy Efficiency Certificate)</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>20/03/2026</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3183,12 +3183,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>AGN RAGNAR</t>
+          <t>AGN LAGERTHA</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>9148104</t>
+          <t>9013000</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3198,12 +3198,12 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>SC (Cargo Ship Safety Construction Certificate)</t>
+          <t>IHM (Statement of Compliance on Inventory of Hazardous Materials)</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>01/07/2026</t>
+          <t>20/03/2026</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3215,12 +3215,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>AGN RAGNAR</t>
+          <t>AGN LAGERTHA</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>9148104</t>
+          <t>9013000</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3230,12 +3230,12 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>SE (Cargo Ship Safety Equipment Certificate)</t>
+          <t>IMSBC (Interim Document of Compliance for the Carriage of Solid Bulk Cargoes (with EXE))</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>01/07/2026</t>
+          <t>20/03/2026</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3247,12 +3247,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>AGN RAGNAR</t>
+          <t>AGN LAGERTHA</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>9148104</t>
+          <t>9013000</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>SMC (Safety Management Certificate)</t>
+          <t>IOPP (International Oil Pollution Prevention Certificate - Other than Oil Tanker)</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>20/03/2026</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3279,12 +3279,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>AGN RAGNAR</t>
+          <t>AGN LAGERTHA</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>9148104</t>
+          <t>9013000</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>SR (Cargo Ship Safety Radio Certificate)</t>
+          <t>ISPP (International Sewage Pollution Prevention Certificate)</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>01/07/2026</t>
+          <t>20/03/2026</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3311,27 +3311,27 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>AGRAFENA</t>
+          <t>AGN LAGERTHA</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>9100097</t>
+          <t>9013000</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>PANAMA</t>
+          <t>PALAU</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>CICA (Certificate of Inspection of Crew Accommodation)</t>
+          <t>ISPP (International Sewage Pollution Prevention Certificate)</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>15/03/2024</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3343,27 +3343,27 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>AGRAFENA</t>
+          <t>AGN LAGERTHA</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>9100097</t>
+          <t>9013000</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>PANAMA</t>
+          <t>PALAU</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>CICA (Certificate of Inspection of Crew Accommodation)</t>
+          <t>ISSC (International Ship Security Certificate)</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>11/11/2025</t>
+          <t>20/03/2026</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3375,27 +3375,27 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>AHMET CAN</t>
+          <t>AGN LAGERTHA</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>9368182</t>
+          <t>9013000</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>PANAMA</t>
+          <t>PALAU</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>BWM (International Ballast Water Management Certificate)</t>
+          <t>ITC (International Tonnage Certificate)</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>15/04/2024</t>
+          <t>20/03/2026</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3407,27 +3407,27 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>AHMET CAN</t>
+          <t>AGN LAGERTHA</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>9368182</t>
+          <t>9013000</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>PANAMA</t>
+          <t>PALAU</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>CICA (Certificate of Inspection of Crew Accommodation)</t>
+          <t>LL ( International Load Line Certificate )</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>07/07/2023</t>
+          <t>20/03/2026</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3439,27 +3439,27 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>AHMET CAN</t>
+          <t>AGN LAGERTHA</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>9368182</t>
+          <t>9013000</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>PANAMA</t>
+          <t>PALAU</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>DANG (Certificate of Compliance with Special Requirements for Ships Carrying Dangerous Goods)</t>
+          <t>MLC (Maritime Labour Certificate)</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>08/04/2024</t>
+          <t>20/03/2026</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3471,27 +3471,27 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>AHMET CAN</t>
+          <t>AGN LAGERTHA</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>9368182</t>
+          <t>9013000</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>PANAMA</t>
+          <t>PALAU</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>GPP (Garbage Pollution Prevention Statement of Compliance)</t>
+          <t>SC (Cargo Ship Safety Construction Certificate)</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>08/04/2024</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3503,27 +3503,27 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>AHMET CAN</t>
+          <t>AGN LAGERTHA</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>9368182</t>
+          <t>9013000</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>PANAMA</t>
+          <t>PALAU</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>IAPP (International Air Pollution Prevention Certificate)</t>
+          <t>SE (Cargo Ship Safety Equipment Certificate)</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>08/04/2024</t>
+          <t>30/03/2026</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3535,27 +3535,27 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>AHMET CAN</t>
+          <t>AGN LAGERTHA</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>9368182</t>
+          <t>9013000</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>PANAMA</t>
+          <t>PALAU</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>IHM (Statement of Compliance on Inventory of Hazardous Materials)</t>
+          <t>SMC (Safety Management Certificate)</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>15/04/2024</t>
+          <t>20/03/2026</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3567,27 +3567,27 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>AHMET CAN</t>
+          <t>AGN LAGERTHA</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>9368182</t>
+          <t>9013000</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>PANAMA</t>
+          <t>PALAU</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>IMSBC (Document of Compliance for the Carriage of Solid Bulk Cargoes)</t>
+          <t>SR (Cargo Ship Safety Radio Certificate)</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>08/04/2024</t>
+          <t>20/03/2026</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3599,27 +3599,27 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>AHMET CAN</t>
+          <t>AGN RAGNAR</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>9368182</t>
+          <t>9148104</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>PANAMA</t>
+          <t>PALAU</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>IOPP (International Oil Pollution Prevention Certificate)</t>
+          <t>BWM (International Ballast Water Management Certificate)</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>08/04/2024</t>
+          <t>01/07/2026</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3631,27 +3631,27 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>AHMET CAN</t>
+          <t>AGN RAGNAR</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>9368182</t>
+          <t>9148104</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>PANAMA</t>
+          <t>PALAU</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>ISPP (International Sewage Pollution Prevention Certificate)</t>
+          <t>CL (Certificate of Classification)</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>08/04/2024</t>
+          <t>01/07/2026</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
